--- a/data/estad_portales/Rendimiento_p2.xlsx
+++ b/data/estad_portales/Rendimiento_p2.xlsx
@@ -427,25 +427,25 @@
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="2" t="str">
-        <v>14/08/2026</v>
+        <v>21/08/2026</v>
       </c>
       <c r="B2" s="2">
-        <v>18549</v>
+        <v>16570</v>
       </c>
       <c r="C2" s="2">
-        <v>542</v>
+        <v>630</v>
       </c>
       <c r="D2" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="str">
         <v/>
@@ -453,25 +453,25 @@
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="2" t="str">
-        <v>15/08/2026</v>
+        <v>22/08/2026</v>
       </c>
       <c r="B3" s="2">
-        <v>15340</v>
+        <v>17063</v>
       </c>
       <c r="C3" s="2">
-        <v>409</v>
+        <v>585</v>
       </c>
       <c r="D3" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
         <v>5</v>
       </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="str">
         <v/>
@@ -479,25 +479,25 @@
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="2" t="str">
-        <v>16/08/2026</v>
+        <v>23/08/2026</v>
       </c>
       <c r="B4" s="2">
-        <v>19335</v>
+        <v>18921</v>
       </c>
       <c r="C4" s="2">
-        <v>535</v>
+        <v>640</v>
       </c>
       <c r="D4" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="str">
         <v/>
@@ -505,22 +505,22 @@
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="2" t="str">
-        <v>17/08/2026</v>
+        <v>24/08/2026</v>
       </c>
       <c r="B5" s="2">
-        <v>20643</v>
+        <v>21514</v>
       </c>
       <c r="C5" s="2">
-        <v>790</v>
+        <v>744</v>
       </c>
       <c r="D5" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -531,25 +531,25 @@
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="2" t="str">
-        <v>18/08/2026</v>
+        <v>25/08/2026</v>
       </c>
       <c r="B6" s="2">
-        <v>18416</v>
+        <v>18131</v>
       </c>
       <c r="C6" s="2">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="D6" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="str">
         <v/>
@@ -557,25 +557,25 @@
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="2" t="str">
-        <v>19/08/2026</v>
+        <v>26/08/2026</v>
       </c>
       <c r="B7" s="2">
-        <v>20456</v>
+        <v>18120</v>
       </c>
       <c r="C7" s="2">
-        <v>743</v>
+        <v>661</v>
       </c>
       <c r="D7" s="2">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="str">
         <v/>
@@ -583,25 +583,25 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="2" t="str">
-        <v>20/08/2026</v>
+        <v>27/08/2026</v>
       </c>
       <c r="B8" s="2">
-        <v>18676</v>
+        <v>18099</v>
       </c>
       <c r="C8" s="2">
-        <v>698</v>
+        <v>632</v>
       </c>
       <c r="D8" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="str">
         <v/>
